--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942613</v>
+        <v>121942628</v>
       </c>
       <c r="B2" t="n">
-        <v>58001</v>
+        <v>57376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942628</v>
+        <v>121942613</v>
       </c>
       <c r="B3" t="n">
-        <v>57376</v>
+        <v>58001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942628</v>
+        <v>121942604</v>
       </c>
       <c r="B2" t="n">
-        <v>57376</v>
+        <v>58034</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121942604</v>
+        <v>121942628</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>57376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942604</v>
+        <v>121942628</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>121942613</v>
       </c>
       <c r="B3" t="n">
-        <v>58001</v>
+        <v>58009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121942628</v>
+        <v>121942604</v>
       </c>
       <c r="B4" t="n">
-        <v>57376</v>
+        <v>58042</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942628</v>
+        <v>121942613</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>58009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942613</v>
+        <v>121942628</v>
       </c>
       <c r="B3" t="n">
-        <v>58009</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942613</v>
+        <v>121942604</v>
       </c>
       <c r="B2" t="n">
-        <v>58009</v>
+        <v>58042</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942628</v>
+        <v>121942613</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>58009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121942604</v>
+        <v>121942628</v>
       </c>
       <c r="B4" t="n">
-        <v>58042</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121942604</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>58046</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942613</v>
+        <v>121942628</v>
       </c>
       <c r="B3" t="n">
-        <v>58009</v>
+        <v>57388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121942628</v>
+        <v>121942613</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>58013</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942604</v>
+        <v>121942613</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942628</v>
+        <v>121942604</v>
       </c>
       <c r="B3" t="n">
-        <v>57388</v>
+        <v>58050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121942613</v>
+        <v>121942628</v>
       </c>
       <c r="B4" t="n">
-        <v>58013</v>
+        <v>57391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942613</v>
+        <v>121942628</v>
       </c>
       <c r="B2" t="n">
-        <v>58017</v>
+        <v>57393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942604</v>
+        <v>121942613</v>
       </c>
       <c r="B3" t="n">
-        <v>58050</v>
+        <v>58019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121942628</v>
+        <v>121942604</v>
       </c>
       <c r="B4" t="n">
-        <v>57391</v>
+        <v>58052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942628</v>
+        <v>121942613</v>
       </c>
       <c r="B2" t="n">
-        <v>57393</v>
+        <v>58019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942613</v>
+        <v>121942604</v>
       </c>
       <c r="B3" t="n">
-        <v>58019</v>
+        <v>58052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121942604</v>
+        <v>121942628</v>
       </c>
       <c r="B4" t="n">
-        <v>58052</v>
+        <v>57393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121942613</v>
+        <v>121942628</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>57393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121942628</v>
+        <v>121942613</v>
       </c>
       <c r="B3" t="n">
-        <v>57393</v>
+        <v>58019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>130322361</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>130322361</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>130322361</v>
       </c>
       <c r="B5" t="n">
-        <v>57981</v>
+        <v>57989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>130322361</v>
       </c>
       <c r="B5" t="n">
-        <v>57989</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17541-2021 artfynd.xlsx
+++ b/artfynd/A 17541-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>130322361</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
